--- a/riobamba-censo-data/shp/plataforma_e.xlsx
+++ b/riobamba-censo-data/shp/plataforma_e.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -498,11 +498,12 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,25 +534,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>edad0_14</t>
+          <t>edad0_4</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>edad15_29</t>
+          <t>edad5_11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>edad30_44</t>
+          <t>edad12_17</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>edad45_64</t>
+          <t>edad18_29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>edad30_64</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>edad65mas</t>
         </is>
@@ -578,18 +584,21 @@
         <v>22</v>
       </c>
       <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
-        <v>28</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4</v>
-      </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="J2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -614,18 +623,21 @@
         <v>2</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -650,23 +662,26 @@
         <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
         <v>29</v>
       </c>
-      <c r="H4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
       <c r="J4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K4" t="n">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>